--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487889_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487889_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>M. TIKHONENKO ANDRIYASHCHENKO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5534</v>
+        <v>4.3606</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2574</v>
+        <v>3.2001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.296</v>
+        <v>1.1606</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5887</v>
+        <v>2.3326</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9273</v>
+        <v>1.081</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6614</v>
+        <v>1.2516</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5111</v>
+        <v>2.6429</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3152</v>
+        <v>0.8974</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1959</v>
+        <v>1.7455</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0776</v>
+        <v>-0.3103</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3879</v>
+        <v>0.1836</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4655</v>
+        <v>-0.4939</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0386</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9316</v>
+        <v>-0.0266</v>
       </c>
       <c r="U2" t="n">
-        <v>0.107</v>
+        <v>0.8436</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.1145</v>
+        <v>0.3786</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.1852</v>
+        <v>0.5838</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0708</v>
+        <v>-0.2052</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. TIKHONENKO ANDRIYASHCHENKO</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2833</v>
+        <v>3.1034</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5338</v>
+        <v>0.5726</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7495000000000001</v>
+        <v>2.5308</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3326</v>
+        <v>2.5887</v>
       </c>
       <c r="H3" t="n">
-        <v>1.081</v>
+        <v>0.9273</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2516</v>
+        <v>1.6614</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6429</v>
+        <v>1.5111</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8974</v>
+        <v>1.3152</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7455</v>
+        <v>0.1959</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3103</v>
+        <v>1.0776</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1836</v>
+        <v>-0.3879</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4939</v>
+        <v>1.4655</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2603</v>
+        <v>0.5886</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6929</v>
+        <v>0.2467</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4326</v>
+        <v>0.3419</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3786</v>
+        <v>-1.1145</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5838</v>
+        <v>-1.1852</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2052</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4029</v>
+        <v>1.75</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8208</v>
+        <v>0.3208</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2237</v>
+        <v>1.4292</v>
       </c>
       <c r="G4" t="n">
         <v>0.5819</v>
@@ -766,13 +766,13 @@
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2421</v>
+        <v>1.105</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3734</v>
+        <v>-0.2319</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1313</v>
+        <v>1.3369</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1451</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. FAIAL</t>
+          <t>I. CASAS GARRIDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0446</v>
+        <v>-0.4044</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.6218</v>
+        <v>-2.793</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5772</v>
+        <v>2.3886</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9437</v>
+        <v>-0.6345</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1003</v>
+        <v>-0.7292</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8434</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.711</v>
+        <v>-1.4385</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.1859</v>
+        <v>-0.676</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.5251</v>
+        <v>-0.7625</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7673</v>
+        <v>0.8041</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0856</v>
+        <v>-0.0532</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6817</v>
+        <v>0.8572</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.0613</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4352</v>
+        <v>-0.3138</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1131</v>
+        <v>0.2525</v>
       </c>
       <c r="V6" t="n">
-        <v>2.0131</v>
+        <v>0.7076</v>
       </c>
       <c r="W6" t="n">
-        <v>2.565</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5518999999999999</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>L. FAIAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1934</v>
+        <v>-0.4677</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2439</v>
+        <v>-2.5751</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4373</v>
+        <v>2.1074</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7773</v>
+        <v>-2.9437</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1086</v>
+        <v>-2.1003</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6686</v>
+        <v>-0.8434</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1168</v>
+        <v>-3.711</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0384</v>
+        <v>-2.1859</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0784</v>
+        <v>-1.5251</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.894</v>
+        <v>0.7673</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.147</v>
+        <v>0.0856</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.747</v>
+        <v>0.6817</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4164</v>
+        <v>0.2548</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1678</v>
+        <v>-0.3886</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2486</v>
+        <v>0.6433</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.0131</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.565</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5518999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. CASAS GARRIDO</t>
+          <t>G. BOAHEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6882</v>
+        <v>-0.7634</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9887</v>
+        <v>-3.7222</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3005</v>
+        <v>2.9588</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6345</v>
+        <v>-2.249</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7292</v>
+        <v>-2.3739</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1249</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4385</v>
+        <v>-2.555</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.676</v>
+        <v>-2.7452</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7625</v>
+        <v>0.1902</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8041</v>
+        <v>0.306</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0532</v>
+        <v>0.3713</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8572</v>
+        <v>-0.0653</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4162</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>-3.3299</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3451</v>
+        <v>1.3986</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.0485</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1644</v>
+        <v>1.4471</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7076</v>
+        <v>1.96</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.2112</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7076</v>
+        <v>-0.2512</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0355</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.682</v>
+        <v>-1.2486</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6465</v>
+        <v>0.3822</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7201</v>
@@ -1156,13 +1156,13 @@
         <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0196</v>
+        <v>0.1887</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5376</v>
+        <v>-0.1043</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5572</v>
+        <v>0.293</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1675</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MORENO POZA</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2948</v>
+        <v>-0.9202</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9046</v>
+        <v>-0.4828</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6098</v>
+        <v>-0.4373</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4398</v>
+        <v>-0.7773</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0493</v>
+        <v>-0.1086</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.489</v>
+        <v>-0.6686</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1359</v>
+        <v>0.1168</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0576</v>
+        <v>0.0384</v>
       </c>
       <c r="L10" t="n">
         <v>0.0784</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5757</v>
+        <v>-0.894</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0083</v>
+        <v>-0.147</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5674</v>
+        <v>-0.747</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2487</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3607</v>
+        <v>0.6896</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0842</v>
+        <v>0.441</v>
       </c>
       <c r="U10" t="n">
-        <v>0.445</v>
+        <v>0.2486</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7996</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. BOAHEN</t>
+          <t>J. MORENO POZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8691</v>
+        <v>-1.1727</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7985</v>
+        <v>-1.8999</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9294</v>
+        <v>0.7272</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.249</v>
+        <v>-0.4398</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3739</v>
+        <v>0.0493</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1249</v>
+        <v>-0.489</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.555</v>
+        <v>0.1359</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.7452</v>
+        <v>0.0576</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1902</v>
+        <v>0.0784</v>
       </c>
       <c r="M11" t="n">
-        <v>0.306</v>
+        <v>-0.5757</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3713</v>
+        <v>-0.0083</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0653</v>
+        <v>-0.5674</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8731</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.3299</v>
+        <v>-1.2487</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2929</v>
+        <v>0.4829</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1248</v>
+        <v>-0.0795</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4178</v>
+        <v>0.5624</v>
       </c>
       <c r="V11" t="n">
-        <v>1.96</v>
+        <v>-0.7996</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2112</v>
+        <v>-0.7076</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2512</v>
+        <v>-0.092</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0383</v>
+        <v>-1.9665</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4761</v>
+        <v>-1.3456</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5622</v>
+        <v>-0.621</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2073</v>
@@ -1390,13 +1390,13 @@
         <v>0.4162</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2473</v>
+        <v>-0.1755</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1057</v>
+        <v>0.0248</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1416</v>
+        <v>-0.2003</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7219</v>
+        <v>-2.6893</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2558</v>
+        <v>-1.9295</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4661</v>
+        <v>-0.7597</v>
       </c>
       <c r="G13" t="n">
         <v>-2.6755</v>
@@ -1468,13 +1468,13 @@
         <v>1.0406</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5345</v>
+        <v>1.5671</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.019</v>
+        <v>0.3072</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5534</v>
+        <v>1.2599</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3727</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.4381</v>
+        <v>0.1715000000000004</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.5132</v>
+        <v>-11.9032</v>
       </c>
       <c r="F14" t="n">
-        <v>12.0751</v>
+        <v>12.0749</v>
       </c>
       <c r="G14" t="n">
         <v>-6.8583</v>
@@ -1519,7 +1519,7 @@
         <v>3.388000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.8972</v>
+        <v>-4.897199999999999</v>
       </c>
       <c r="K14" t="n">
         <v>-7.5301</v>
@@ -1534,10 +1534,10 @@
         <v>-2.7161</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7552999999999997</v>
+        <v>0.7553</v>
       </c>
       <c r="P14" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>-5.551115123125783e-17</v>
       </c>
       <c r="Q14" t="n">
         <v>-10.4059</v>
@@ -1546,19 +1546,19 @@
         <v>10.4059</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9601</v>
+        <v>6.569799999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.783000000000001</v>
+        <v>-0.1735</v>
       </c>
       <c r="U14" t="n">
-        <v>6.743099999999999</v>
+        <v>6.7432</v>
       </c>
       <c r="V14" t="n">
         <v>0.4599000000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>3.5734</v>
+        <v>3.573399999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-3.1133</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0958</v>
+        <v>6.5165</v>
       </c>
       <c r="E15" t="n">
         <v>1.7772</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3186</v>
+        <v>4.7394</v>
       </c>
       <c r="G15" t="n">
         <v>4.7253</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2577</v>
+        <v>0.1631</v>
       </c>
       <c r="T15" t="n">
         <v>-1.2305</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9729</v>
+        <v>1.3936</v>
       </c>
       <c r="V15" t="n">
         <v>1.8362</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5296</v>
+        <v>3.8486</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8659</v>
+        <v>0.4373</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6637</v>
+        <v>3.4113</v>
       </c>
       <c r="G16" t="n">
         <v>2.6293</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2322</v>
+        <v>0.5513</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5153</v>
+        <v>0.0867</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2831</v>
+        <v>0.4645</v>
       </c>
       <c r="V16" t="n">
         <v>0.4599</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2486</v>
+        <v>2.8763</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9814</v>
+        <v>2.0885</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2672</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>2.8138</v>
@@ -1780,13 +1780,13 @@
         <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4431</v>
+        <v>-0.8153</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3701</v>
+        <v>-1.263</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.073</v>
+        <v>0.4476</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1627</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5188</v>
+        <v>1.7419</v>
       </c>
       <c r="E18" t="n">
         <v>0.0097</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5091</v>
+        <v>1.7322</v>
       </c>
       <c r="G18" t="n">
         <v>2.6574</v>
@@ -1858,13 +1858,13 @@
         <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0437</v>
+        <v>0.1794</v>
       </c>
       <c r="T18" t="n">
         <v>-1.0348</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9911</v>
+        <v>1.2142</v>
       </c>
       <c r="V18" t="n">
         <v>-0.4706</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. HERNANDEZ RODRIGUEZ</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1484</v>
+        <v>0.794</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1305</v>
+        <v>-0.9684</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2789</v>
+        <v>1.7624</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2857</v>
+        <v>1.2945</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1429</v>
+        <v>1.7721</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1429</v>
+        <v>-0.4776</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.0742</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.8782</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.1959</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2857</v>
+        <v>0.2203</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1429</v>
+        <v>0.8938</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1429</v>
+        <v>-0.6735</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.3991</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1305</v>
+        <v>-1.002</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0391</v>
+        <v>0.6029</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.046</v>
+        <v>0.3149</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.046</v>
+        <v>0.3149</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>M. HERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1449</v>
+        <v>0.2071</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0755</v>
+        <v>-0.1305</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9306</v>
+        <v>0.3376</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2945</v>
+        <v>0.2857</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7721</v>
+        <v>0.1429</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4776</v>
+        <v>0.1429</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0742</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8782</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1959</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2203</v>
+        <v>0.2857</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8938</v>
+        <v>0.1429</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6735</v>
+        <v>0.1429</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4162</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3381</v>
+        <v>-0.0326</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1091</v>
+        <v>-0.1305</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2289</v>
+        <v>0.0979</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3149</v>
+        <v>-0.046</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3149</v>
+        <v>-0.046</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4933</v>
+        <v>-0.4052</v>
       </c>
       <c r="E21" t="n">
         <v>-0.5049</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0116</v>
+        <v>0.0997</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3591</v>
@@ -2092,13 +2092,13 @@
         <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2799</v>
+        <v>-0.1918</v>
       </c>
       <c r="T21" t="n">
         <v>-0.5096000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2297</v>
+        <v>0.3178</v>
       </c>
       <c r="V21" t="n">
         <v>0.3538</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4925</v>
+        <v>-1.7742</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9902</v>
+        <v>-3.5616</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4977</v>
+        <v>1.7874</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5375</v>
@@ -2170,13 +2170,13 @@
         <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3712</v>
+        <v>0.3471</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4567</v>
+        <v>-0.0281</v>
       </c>
       <c r="U22" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.3751</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5294</v>
+        <v>-1.9667</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1753</v>
+        <v>-2.3897</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3541</v>
+        <v>0.4229</v>
       </c>
       <c r="G23" t="n">
         <v>0.0192</v>
@@ -2248,13 +2248,13 @@
         <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3197</v>
+        <v>0.243</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2519</v>
+        <v>-0.4662</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0678</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2289</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.4428</v>
+        <v>-5.114</v>
       </c>
       <c r="E24" t="n">
         <v>-8.832599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>3.3898</v>
+        <v>3.7186</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6705</v>
@@ -2326,13 +2326,13 @@
         <v>1.8731</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0476</v>
+        <v>0.2812</v>
       </c>
       <c r="T24" t="n">
         <v>-1.1653</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1177</v>
+        <v>1.4465</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5165</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.438299999999999</v>
+        <v>6.7243</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.0748</v>
+        <v>-12.075</v>
       </c>
       <c r="F25" t="n">
-        <v>14.5131</v>
+        <v>18.7993</v>
       </c>
       <c r="G25" t="n">
         <v>6.858099999999999</v>
@@ -2404,13 +2404,13 @@
         <v>10.406</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.9601</v>
+        <v>0.3263</v>
       </c>
       <c r="T25" t="n">
-        <v>-6.743200000000001</v>
+        <v>-6.7433</v>
       </c>
       <c r="U25" t="n">
-        <v>2.7832</v>
+        <v>7.0693</v>
       </c>
       <c r="V25" t="n">
         <v>-0.4599</v>
